--- a/mistral_translate_work/split_by_prompt/excel/lore/lang_infodisplay/lang_infodisplay__lore__part_0001.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/lore/lang_infodisplay/lang_infodisplay__lore__part_0001.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Ảnh Rừng Mờ chắc chắn là kho báu vĩ đại nhất ở Huanglong, không vùng đất nào sánh được về sự phong phú loài.
+          <t>Rừng Mờ Ảnh chắc chắn là kho báu vĩ đại nhất ở Huanglong, không vùng đất nào sánh được về sự phong phú loài.
 Chỉ cần đứng trước cổng vào, ta đã nghe rõ tiếng thì thầm của cây cối và lời mời gọi của chúng.
 May mắn thay, những dữ liệu thực vật quý giá này lại nằm trong tầm tay! Thứ mà con tinh tinh đang cầm trên tay chính là hình ảnh của cây mã đề tên XXX trong tài liệu.
 Ghi chép cho thấy loại quả này, được cả già lẫn trẻ ưa chuộng, từng được trồng rộng rãi trước Thảm Họa.
@@ -730,8 +730,8 @@
           <t>Sau khi từ biệt Xxx, tôi tiến về mục tiêu quan trọng nhất – Khu Rừng Giam Cầm.
 Đó là một cái cây cao hơn 200 mét, và bất cứ ai cũng có thể cảm nhận được hơi thở phiêu lưu toát ra từ gã khổng lồ này. Sự hiện diện của nó dường như tượng trưng cho sức sống vô tận, và tôi cùng Xxx bị cuốn hút bởi sinh khí ấy như ánh nắng buổi chiều. Chúng tôi không kìm được mà nhảy cẫng lên, reo hò.
 Nhưng càng đến gần cây, âm thanh của thực vật càng trở nên bất an. Ngay cả những đám bèo dưới chân cũng phát ra tiếng động kỳ lạ.
-Rare khi tôi bắt gặp hiện tượng này ngoài phạm vi bức xạ của Tacet Field. Tìm ra nguồn gốc của nó có thể dẫn đến lời giải cho việc tại sao cây cối khắp Rừng Mờ – cả Khu Rừng Giam Cầm lẫn Xxx vừa rồi – lại cao lớn đến vậy.
-Vậy còn chần chừ gì nữa? Stand dậy đi ngay còn hơn ngồi nói suông!</t>
+Hiếm khi tôi bắt gặp hiện tượng này ngoài phạm vi bức xạ của Tổ Tacet. Tìm ra nguồn gốc của nó có thể dẫn đến lời giải cho việc tại sao cây cối khắp Rừng Mờ – cả Khu Rừng Giam Cầm lẫn Xxx vừa rồi – lại cao lớn đến vậy.
+Vậy còn chần chừ gì nữa? Đứng dậy đi ngay còn hơn ngồi nói suông!</t>
         </is>
       </c>
     </row>
@@ -799,8 +799,8 @@
       <c r="M5" t="inlineStr">
         <is>
           <t>Ôi, không biết lần cuối tôi phải di chuyển vất vả như thế này là khi nào.
-Vỏ xe tôi đạp lên khi nhảy xuống lại giấu một Tacet Field XXX bất ngờ. Đây là lần đầu tôi thấy một Tacet Field dai dẳng đến vậy, nó đuổi theo như thể thực sự nổi giận. Nó đuổi tôi từ Khu Rừng Giam Cầm đến tận đây trước khi tôi kịp thoát thân.
-Nhưng nơi này đã gần Tacet Field, đất đai cằn cỗi, cây cối chỉ còn những âm thanh đau đớn. Tôi chẳng thể làm gì cho chúng trong tình trạng này. Right phấn chấn lên! Suy tàn và diệt vong cũng là một phần của sinh thái. Tự nhiên không phải lúc nào cũng dịu dàng, và nhiệm vụ của tôi là phát hiện và chứng kiến điều đó.</t>
+Vỏ xe tôi đạp lên khi nhảy xuống lại giấu một Tổ Tacet XXX bất ngờ. Đây là lần đầu tôi thấy một Tổ Tacet dai dẳng đến vậy, nó đuổi theo như thể thực sự nổi giận. Nó đuổi tôi từ Khu Rừng Giam Cầm đến tận đây trước khi tôi kịp thoát thân.
+Nhưng nơi này đã gần Tổ Tacet, đất đai cằn cỗi, cây cối chỉ còn những âm thanh đau đớn. Tôi chẳng thể làm gì cho chúng trong tình trạng này. Phải phấn chấn lên! Suy tàn và diệt vong cũng là một phần của sinh thái. Tự nhiên không phải lúc nào cũng dịu dàng, và nhiệm vụ của tôi là phát hiện và chứng kiến điều đó.</t>
         </is>
       </c>
     </row>
@@ -869,8 +869,8 @@
       <c r="M6" t="inlineStr">
         <is>
           <t>Môi trường của Confinement Woods còn kỳ diệu hơn cả dự đoán. Một hệ sinh thái tán cây độc đáo đã hình thành quanh những cành khổng lồ của cây cổ thụ này.
-Theo điều tra của tôi, các nhánh cây chứa đựng nguồn Năng Lượng Synergy dồi dào bên trong. Năng lượng thu thập từ khắp khu vực Dim Forest di chuyển từ ngọn cây xuống toàn bộ thân cây. Dưới tác động của năng lượng này, một cây khổng lồ như vậy đã được hình thành. Và chính nhờ những nguồn năng lượng ấy, cây đã tái tạo nên một hệ sinh thái hoàn toàn khác biệt. Có lẽ do những tiếng gầm dữ dội thỉnh thoảng vang lên từ bên trong thân cây, nên không có dấu hiệu hoạt động của các MO hay TD lớn. Điều này tạo điều kiện cho thực vật phát triển mạnh mẽ và cho phép Remnant Mutterfly tồn tại.
-Skills của Synergy Giả tạo ra cây khổng lồ này rất giống với tôi. Tôi đoán anh ấy cũng là một người yêu thiên nhiên. Nếu không, dù có sự hỗ trợ của nhạc cụ âm thanh trên ngọn cây, cũng khó lòng tạo ra một cây khổng lồ phức tạp đến vậy.
+Theo điều tra của tôi, các nhánh cây chứa đựng nguồn Resonance Energy dồi dào bên trong. Năng lượng thu thập từ khắp khu vực Dim Forest di chuyển từ ngọn cây xuống toàn bộ thân cây. Dưới tác động của năng lượng này, một cây khổng lồ như vậy đã được hình thành. Và chính nhờ những nguồn năng lượng ấy, cây đã tái tạo nên một hệ sinh thái hoàn toàn khác biệt. Có lẽ do những tiếng gầm dữ dội thỉnh thoảng vang lên từ bên trong thân cây, nên không có dấu hiệu hoạt động của các MO hay TD lớn. Điều này tạo điều kiện cho thực vật phát triển mạnh mẽ và cho phép Remnant Mutterfly tồn tại.
+Kỹ năng của Resonator tạo ra cây khổng lồ này rất giống với tôi. Tôi đoán anh ấy cũng là một người yêu thiên nhiên. Nếu không, dù có sự hỗ trợ của nhạc cụ âm thanh trên ngọn cây, cũng khó lòng tạo ra một cây khổng lồ phức tạp đến vậy.
 Để thuận tiện cho các chuyến thám hiểm sau này, tôi đã tạo một chút trang trí phát quang trên cành của Confinement Woods làm dấu hiệu. Điều này sẽ giúp các chuyến nghiên cứu sau này hiệu quả hơn. Vậy là đã đến lúc lên đường, khám phá sâu hơn vào lòng Confinement Woods!</t>
         </is>
       </c>
@@ -946,7 +946,7 @@
 [Tiếng Hoochief kêu chít chít]
 Jueyuan: Con khỉ đột xấu xa! Đó không phải thức ăn!
 [Tiếng Hoochief chế nhạo]
-Jueyuan: Stop ngay -- (giọng trầm xuống, xa dần)</t>
+Jueyuan: Dừng lại ngay -- (giọng trầm xuống, xa dần)</t>
         </is>
       </c>
     </row>
@@ -1093,14 +1093,14 @@
 "Tàn tích gợi nhớ giấc mơ xưa của thành phố cũ,
 Tương lai chẳng bao giờ ta thấy, chỉ có quá khứ để khóc thương."
 - Giấc mơ về quá khứ, du hành xuyên thời gian. Vở kịch mới lạ, nhập vai &lt;i&gt;Vầng trăng trên bầu trời&lt;/i&gt; chính thức công chiếu.
-Hội Truyện tranh Tiancheng lần thứ Năm sắp diễn ra.
+Hội nghị Truyện tranh Thiên Thành lần thứ Năm sắp diễn ra.
 Tác phẩm truyện tranh mới nhất của Qinghe và Shongsheng &lt;i&gt;Cơn bão thành cổ&lt;/i&gt; ra mắt.
-Một đêm opera vừa thanh nhã, vừa trần tục.
-[Hướng dẫn dành cho khán giả]
-1. Nhà hát Tiancheng là nhà hát mở, xin vui lòng tuân thủ trật tự công cộng.
+Một đêm opera vừa thanh tao, vừa trần tục.
+[Hướng dẫn khán giả]
+1. Nhà hát Thiên Thành là nhà hát mở, xin vui lòng tuân thủ trật tự công cộng.
 2. Trong suốt buổi biểu diễn, bạn có thể ra vào tự do, nhưng xin giữ im lặng.
 3. Nghiêm cấm xâm phạm sân khấu. Người vi phạm sẽ bị giao cho Lực lượng Mourn Guards.
-4. Giữ gìn môi trường công cộng là trách nhiệm của mọi người. Sau khi the performance, xin mang theo rác thải cá nhân.</t>
+4. Giữ gìn môi trường công cộng là trách nhiệm của mọi người. Sau buổi biểu diễn, xin mang theo rác thải cá nhân.</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>&lt;i&gt;Cửa hàng Âm Thanh *Trở Về Giấc Mơ*&lt;/i&gt;</t>
+          <t>&lt;i&gt;Cửa Hàng Âm Thanh *Trở Về Giấc Mơ*&lt;/i&gt;</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
 Con quạ kêu trên tháp phía tây, bóng trúc in trên khung cửa sổ.
 - Cuối Thu 5000 xu Tacetite
 Tíc tắc, tíc tắc, mái hiên đang rên rỉ.
-- Night Không Trăng 9999 xu Tacetite</t>
+- Đêm Không Trăng 9999 xu Tacetite</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
         <is>
           <t>Tiêu chuẩn hóa, trôi chảy và công nghiệp hóa.
 Khai thác Tacetite hiệu quả, tinh luyện Wutherium Fluid chính xác.
-Shipping an toàn, sản xuất tuân thủ quy định.
+Vận chuyển an toàn, sản xuất tuân thủ quy định.
 Bộ Phát Triển</t>
         </is>
       </c>
@@ -1387,14 +1387,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>159 A. L. December 31
-Recorder: Huaijin
+          <t>159 A. L. Ngày 31 tháng 12
+Người ghi chép: Huaijin
 Học viện và Bộ đã cùng ban hành phiên bản mới nhất của "Sổ tay Ứng phó Khẩn cấp Rò rỉ Wutheron", và quản đốc nói rằng tôi là người hiểu rõ nhất về năng lượng Tacetite ở đây, nên phải nghiên cứu trước rồi đào tạo cho các công nhân mỏ trong vài ngày tới. Hơn sáu mươi trang hướng dẫn trong hai ngày. Ít nhất cũng phải hai tuần chứ.
 "Đối với nhân sự, thiết bị và vật liệu nhiễm bụi phóng xạ, có thể giảm thiểu thiệt hại bằng cách làm sạch và khử nhiễm."
 "Nước thải nhiễm bẩn phải được xử lý bằng trao đổi ion và không được xả tùy tiện."
-Mấy người ở Học viện chắc là ngu. Nếu đây là sổ tay dành cho thợ mỏ, họ nên dùng từ ngữ đơn giản và dễ hiểu. Trade ion với đủ thứ linh tinh, thợ mỏ nào biết đâu.
+Mấy người ở Học viện chắc là ngu. Nếu đây là sổ tay dành cho thợ mỏ, họ nên dùng từ ngữ đơn giản và dễ hiểu. Trao đổi ion với đủ thứ linh tinh, thợ mỏ nào biết đâu.
 Thôi kệ, dù sao cũng phiền phức, nhưng vì quản đốc, tôi sẽ tóm tắt lại.
-Than ôi, tăng ca vào ngày nghỉ. Thật sự sự mong sau này được nghỉ một tuần.</t>
+Than ôi, tăng ca vào ngày nghỉ. Thật sự mong sau này được nghỉ một tuần.</t>
         </is>
       </c>
     </row>
@@ -1465,8 +1465,8 @@
         <is>
           <t>Dù bóng đêm có nhấn chìm dấu chân ta, chúng ta vẫn có thể và sẽ vươn tới những chân trời xa, miễn là ta luôn giữ vững lòng dũng cảm để khám phá những điều chưa biết.
 - Gửi những chiến binh cống hiến cả đời mình cho những đêm dài
-[Về Garden Zhuông Tang]
-Được thành lập vào năm 155 A.L., Garden Zhuông Tang là nơi tưởng nhớ những chiến binh đã hy sinh vì nền văn minh nhân loại. Mỗi bông hoa trong vườn đều do thủ lĩnh thứ năm của Midnight Rangers, Jiyan, đích thân gieo trồng và tưới tắm. Hạt giống hoa được nhà nghiên cứu thực vật Jueyuan đặc biệt tuyển chọn và lai tạo, phù hợp với địa chất và khí hậu ở Huanglong, đảm bảo tỷ lệ sống sót 100% ngay cả trong điều kiện thời tiết khắc nghiệt, tượng trưng cho tinh thần bất khuất của Huanglong.
+[Về Vườn Chuông Tang]
+Được thành lập vào năm 155 A.L., Vườn Chuông Tang là nơi tưởng nhớ những chiến binh đã hy sinh vì nền văn minh nhân loại. Mỗi bông hoa trong vườn đều do thủ lĩnh thứ năm của Midnight Rangers, Jiyan, đích thân gieo trồng và tưới tắm. Hạt giống hoa được nhà nghiên cứu thực vật Jueyuan đặc biệt tuyển chọn và lai tạo, phù hợp với địa chất và khí hậu ở Huanglong, đảm bảo tỷ lệ sống sót 100% ngay cả trong điều kiện thời tiết khắc nghiệt, tượng trưng cho tinh thần bất khuất của Huanglong.
 Khi đến viếng, người dân cần tôn trọng người đã khuất và không giẫm đạp lên biển hoa. Những kẻ vi phạm sẽ bị giao cho Mourn Guards.</t>
         </is>
       </c>
@@ -1696,13 +1696,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>&lt;Comment Không. 010&gt;
-khóc nức nở...
-&lt;i&gt;Moon Over Sky&lt;/i&gt; thật sự quá cảm động! Tài năng của biên kịch khi tạo ra một câu chuyện như thế này thật đáng kinh ngạc! Tôi không thể ngừng khóc ngay cả sau khi vở kịch kết thúc. Chắc chắn sẽ quay lại xem lần nữa! Hardc thét...
-Phản hồi từ nhà hát: Cảm ơn sự đam mê của bạn dành cho vở diễn. Chúng tôi mong chờ sự hiện diện của bạn vào lúc 6:30 chiều Chủ Nhật tới.
-&lt;Comment Không. 025&gt;
-&lt;i&gt;Old City Storm&lt;/i&gt; thật sự là một món ăn phụ tuyệt vời! Lần tới tôi có thể mang chút tương ớt tự làm của dì tôi và vừa ăn vừa xem không?
-Phản hồi từ nhà hát: Cảm ơn tình cảm của bạn dành cho vở diễn. Ăn uống không bị cấm trong nhà hát, nhưng xin hãy tránh mang đồ ăn có mùi nặng.</t>
+          <t>Bình luận số 010</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1768,7 @@
         <is>
           <t>Đồ thất lạc sau sự kiện &lt;i&gt;Trăng Trên Bầu Trời&lt;/i&gt; lúc 9 giờ tối hôm kia:
 Khuyên tai màu xanh lam                                                                 I, 5    1 chiếc
-Thẻ căn cước của Department Sáng Tạo, Bộ Phát Triển                        I, 6    1 thẻ
+Thẻ căn cước của Cục Sáng Tạo, Bộ Phát Triển                        I, 6    1 thẻ
 Phiếu mua há cảo (có dấu rồng đặc biệt)                                J, 8    2 phiếu</t>
         </is>
       </c>
@@ -1857,10 +1851,10 @@
 [Tài xế giao hàng]
 Mô tả Công Việc:
 Mọi độ tuổi, có bằng lái xe quốc gia, có khả năng thu thập và giao hàng an toàn, nhanh chóng, chính xác theo yêu cầu của công ty.
-Địa Điểm Do Việc:
-Area theo nguyện vọng ứng viên và nhu cầu công việc thực tế.
-Time Do Việc:
-9 tiếng/ngày, 5 ngày/tuần. Bắt đầu từ 7 giờ sáng và kết thúc lúc 7 giờ tối, có 3 tiếng nghỉ giữa ca. Do việc ngoài giờ này được tính là tăng ca và hưởng lương gấp đôi.
+Địa Điểm Làm Việc:
+Khu vực theo nguyện vọng ứng viên và nhu cầu công việc thực tế.
+Thời Gian Làm Việc:
+9 tiếng/ngày, 5 ngày/tuần. Bắt đầu từ 7 giờ sáng và kết thúc lúc 7 giờ tối, có 3 tiếng nghỉ giữa ca. Làm việc ngoài giờ này được tính là tăng ca và hưởng lương gấp đôi.
 Lương và Phúc Lợi:
 1. Trả lương theo sản phẩm, không giới hạn mức tối đa;
 2. Bảo hiểm nhân thọ trọn đời. Xe chuyên dụng được cấp phát. Chỗ ở và đào tạo nghề được cung cấp (bao gồm nhưng không giới hạn nhận diện vật nguy hiểm, trung hòa chất ô nhiễm Tacetite, sơ cứu, v.v.). Đủ điều kiện cấp chứng chỉ kỹ năng;
@@ -1940,14 +1934,14 @@
       <c r="M20" t="inlineStr">
         <is>
           <t>Lịch Trình Tuần Lễ Trao Đổi Học Thuật:
-Chủ Đề: Phân Loại TD và Ý Nghĩa Đối Với Khoa Học Năng Lượng - Ví Dụ Về Prism Vỡ
+Chủ Đề: Phân Loại TD và Ý Nghĩa Đối Với Khoa Học Năng Lượng - Ví Dụ Về Lăng Kính Vỡ
 Địa Điểm: Giảng Đường Số 1
 Diễn Giả: Jansman
-Giới Thiệu Diễn Giả: Nghiên cứu viên trưởng tại Viện Hàn lâm Khoa học Liên bang New, Zhuyên gia Rating tại Trung tâm Nghiên cứu TD, Giám đốc Thường trực tại Viện Sinh Thái Wuthering Waves thuộc Liên bang New. Lĩnh vực nghiên cứu bao gồm phân loại TD, sinh thái học Wuthering Waves, v.v..
+Giới Thiệu Diễn Giả: Nghiên cứu viên trưởng tại Viện Hàn lâm Khoa học Liên bang Mới, Chuyên gia Đánh giá tại Trung tâm Nghiên cứu TD, Giám đốc Thường trực tại Viện Sinh Thái Wuthering Waves thuộc Liên bang Mới. Lĩnh vực nghiên cứu bao gồm phân loại TD, sinh thái học Wuthering Waves, v.v..
 Chủ Đề: Đạo Đức Học Thuật Dưới Góc Nhìn Các Vụ Án Tòa Circuit
-Địa Điểm: Amphitheater
+Địa Điểm: Nhà Hát Vòm
 Diễn Giả: Maichthis
-Giới Thiệu Diễn Giả: Cố vấn Pháp lý Cao cấp của Pioneer Association, Tổng Biên tập Điều hành của &lt;i&gt;Tuần san Khoa học và Công nghệ Phổ thông&lt;/i&gt; thuộc Liên bang New, Nghiên cứu viên Danh dự tại Học viện Huanglong.</t>
+Giới Thiệu Diễn Giả: Cố vấn Pháp lý Cao cấp của Hiệp hội Pioneer, Tổng Biên tập Điều hành của &lt;i&gt;Tuần san Khoa học và Công nghệ Phổ thông&lt;/i&gt; thuộc Liên bang Mới, Nghiên cứu viên Danh dự tại Học viện Huanglong.</t>
         </is>
       </c>
     </row>
@@ -2017,7 +2011,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>【Gợi Ý Tea Dưỡng Sinh】</t>
+          <t>【Gợi Ý Trà Dưỡng Sinh】</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2076,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>"Ánh sáng sẽ không bao giờ tắt tại ngọn hải đăng. Hi mừng trở về, người bạn."</t>
+          <t>"Ánh sáng sẽ không bao giờ tắt tại ngọn hải đăng. Chào mừng trở về, người bạn."</t>
         </is>
       </c>
     </row>
@@ -2151,8 +2145,8 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Qichi Villager, nhân viên bưu điện khu nghiên cứu số 9:
-Gần đây, mật độ Wutheron bất thường đã được ghi nhận ở phía bắc Qichi Village (bao gồm cả khu nghiên cứu số 9). Khả năng cao sẽ xuất hiện đợt sóng TD cỡ nhỏ đến trung bình, Tacet Field đột ngột hoặc các thảm họa khác.
+          <t>Dân làng Qichi, nhân viên bưu điện khu nghiên cứu số 9:
+Gần đây, mật độ Wutheron bất thường đã được ghi nhận ở phía bắc Làng Qichi (bao gồm cả khu nghiên cứu số 9). Khả năng cao sẽ xuất hiện đợt sóng TD cỡ nhỏ đến trung bình, Tổ Tacet đột ngột hoặc các thảm họa khác.
 Vì sự an toàn tính mạng và tài sản của các người, dân làng Qichi khi nhận được thông báo này hãy lập tức chuẩn bị sơ tán, và không mang theo quá nhiều đồ đạc. Đội Midnight Rangers sẽ cử lực lượng hỗ trợ sơ tán các người trong thời gian sớm nhất.
 Nhắc lại, không mang theo quá nhiều đồ đạc, hãy sơ tán nhanh chóng!
 T. B.: Nhân viên bưu điện khu nghiên cứu số 9, hãy chú ý các thông báo tiếp theo.</t>
@@ -2232,13 +2226,13 @@
       <c r="M24" t="inlineStr">
         <is>
           <t>1 phần cá phi lê cay, 1 phần há cảo, 10 xiên
-- lấy khẩu phần Dodgen.
-- con không thích khẩu phần Dodgen... Lấy bánh Guokui được không ạ?
+- lấy khẩu phần nén.
+- con không thích khẩu phần nén... Lấy bánh Guokui được không ạ?
 - mẹ không có thời gian làm Guokui.
 10 lon nước tăng lực
 - đừng lấy mấy thứ nặng nề vô dụng này... lấy thuốc chặn sóng đi. Để dành chỗ!
 - nếu khát thì sao ạ?
-- chịu đựng đi. Đến Tiancheng sẽ có trà sữa mặn mà.
+- chịu đựng đi. Đến Thiên Thành sẽ có trà sữa mặn mà.
 1 bộ Mahjong, 1 lều
 - con yêu, chúng ta không đi cắm trại đâu.
 - nhưng bố nói là đi mà.
@@ -2310,8 +2304,8 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Cây đa cổ thụ "Longwang" nằm ở phía bắc vùng đất Longwang thuộc Trung Nguyên. Theo &lt;i&gt;Biên Niên Thực Vật New Của Huanglong&lt;/i&gt;, tuổi đời của Longwang ước tính từ 1400 đến 1500 năm, và cây vẫn sừng sững sau Thảm Họa. Rễ của nó quấn quýt như trăn, như rồng; những cành cây xù xì giống như móng vuốt sắc nhọn, phô bày vẻ hoang dã.
-Trong những ngày đầu của Chiến tranh Threnody, khi đối mặt với đội quân Tacet Field của Crownless, quân đội Huanglong cùng dân làng Qichi đã hợp sức kháng cự tại đây và giành được chiến thắng quý giá. Cây cổ thụ bất động ấy như tọa độ của mặt đất, trở thành biểu tượng để dựa vào. Chỉ cần Longwang còn đứng vững, Trung Nguyên sẽ hồi sinh.
+          <t>Cây đa cổ thụ "Longwang" nằm ở phía bắc vùng đất Longwang thuộc Trung Nguyên. Theo &lt;i&gt;Biên Niên Thực Vật Mới Của Huanglong&lt;/i&gt;, tuổi đời của Longwang ước tính từ 1400 đến 1500 năm, và cây vẫn sừng sững sau Thảm Họa. Rễ của nó quấn quýt như trăn, như rồng; những cành cây xù xì giống như móng vuốt sắc nhọn, phô bày vẻ hoang dã.
+Trong những ngày đầu của Chiến tranh Threnody, khi đối mặt với đội quân Tổ Tacet của Crownless, quân đội Huanglong cùng dân làng Qichi đã hợp sức kháng cự tại đây và giành được chiến thắng quý giá. Cây cổ thụ bất động ấy như tọa độ của mặt đất, trở thành biểu tượng để dựa vào. Chỉ cần Longwang còn đứng vững, Trung Nguyên sẽ hồi sinh.
 Năm 147 A.L., cư dân làng Qichi, với sự trợ giúp của Tiancheng, đã phục hồi cây cổ thụ và chính thức đặt tên là "Longwang".
 Lưu ý: Xin đừng khắc dấu lên thân hoặc cành cây. Mọi người hãy cùng chung tay bảo vệ cây cổ thụ này.</t>
         </is>
@@ -2378,7 +2372,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>A Diary Không Ký Malee Số 1</t>
+          <t>Nhật Ký Không Ký Tên Số 1</t>
         </is>
       </c>
     </row>
@@ -2448,9 +2442,9 @@
       <c r="M27" t="inlineStr">
         <is>
           <t>Ngày 27
-Việc Dodgem bom kéo dài 3 tiếng. Sau đó dừng lại 2 tiếng, rồi lại tiếp tục thêm 3 tiếng nữa.
+Việc ném bom kéo dài 3 tiếng. Sau đó dừng lại 2 tiếng, rồi lại tiếp tục thêm 3 tiếng nữa.
 Ngày 28
-Việc Dodgem bom kéo dài 3 tiếng. Sau đó dừng lại 2 tiếng, rồi lại tiếp tục thêm 3 tiếng nữa. Sanshui cố ngăn tôi ghi chép lại điều này. Không có quy luật nào cả. Nhưng tôi đếm thời gian bằng cách theo dõi Gui thở dài. Cậu ấy thở dài mỗi nửa tiếng. Tôi biết thói quen của cậu ấy, lúc nào cũng vậy.
+Việc ném bom kéo dài 3 tiếng. Sau đó dừng lại 2 tiếng, rồi lại tiếp tục thêm 3 tiếng nữa. Sanshui cố ngăn tôi ghi chép lại điều này. Không có quy luật nào cả. Nhưng tôi đếm thời gian bằng cách theo dõi Gui thở dài. Cậu ấy thở dài mỗi nửa tiếng. Tôi biết thói quen của cậu ấy, lúc nào cũng vậy.
 Việc ghi chép thời gian là cần thiết. Sẽ có ngày chúng ta thoát khỏi nơi này.</t>
         </is>
       </c>
@@ -2516,7 +2510,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>A Diary Không Ký Malee Số 2</t>
+          <t>Nhật Ký Không Ký Tên Số 2</t>
         </is>
       </c>
     </row>
@@ -2658,7 +2652,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>A Diary Không Ký Malee Số 3</t>
+          <t>Nhật Ký Không Ký Tên Số 3</t>
         </is>
       </c>
     </row>
@@ -2863,7 +2857,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Beware of Bullies!</t>
+          <t>Cẩn Thận Kẻ Bắt Nạt!</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3008,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>~ Hotel An Yên ~</t>
+          <t>~ Khách Sạn An Yên ~</t>
         </is>
       </c>
     </row>
@@ -3103,8 +3097,8 @@
 Đại đội Đặc nhiệm, Tiểu đoàn Tiền tiêu, Trung đoàn Huanglong Midnight Rangers (111162)
 Đội Thám hiểm Địa chất, Học viện Huaglong
 ......
-Phân tích Investigation Result về Mist Bí ẩn:
-Cuộc thám hiểm đã thu thập mẫu sương mù trong đường hầm nối mỏ Hukou và Hazy Depths, phân tích tại hiện trường bằng [Máy Guang phổ Đơn giản] của đội. Dựa trên kết quả test, chúng tôi suy đoán rằng sương mù dường như là một thành phần sinh học, có cấu tạo tương tự như bột vảy trên cánh loài côn trùng cánh vảy, thể hiện tính chất không độc và nhiệt độ thấp.
+Phân tích Kết quả Điều tra về Sương mù Bí ẩn:
+Cuộc thám hiểm đã thu thập mẫu sương mù trong đường hầm nối mỏ Hukou và Hazy Depths, phân tích tại hiện trường bằng [Máy Quang phổ Đơn giản] của đội. Dựa trên kết quả kiểm tra, chúng tôi suy đoán rằng sương mù dường như là một thành phần sinh học, có cấu tạo tương tự như bột vảy trên cánh loài côn trùng cánh vảy, thể hiện tính chất không độc và nhiệt độ thấp.
 Chúng tôi nhận định mối nguy hiểm của sương mù đến từ nhiệt độ thấp:
 ① Ngưng tụ hơi nước do nhiệt độ thấp có thể cản trở tầm nhìn nghiêm trọng, khiến người điều tra mất phương hướng trong khu vực sương mù.
 ② Nhiệt độ thấp có thể trực tiếp ảnh hưởng đến tình trạng sức khỏe của người điều tra, hạ thân nhiệt kéo dài dẫn đến suy giảm thể lực và không thể phản ứng kịp thời trước các mối nguy hiểm.
@@ -3187,7 +3181,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>[Report Event]
+          <t>[Báo cáo Sự kiện]
 Số hiệu: ■■■■
 Điều tra viên: ■■■
 Giám đốc: ■■■, ■■
@@ -3341,7 +3335,7 @@
 ② Nguồn nước có hàm lượng chất không tan tương đối cao. Nghi ngờ có vấn đề ô nhiễm nguồn nước;
 ③ Sự hiện diện hoạt động của MO dẫn đến hàm lượng cao Hợp Chất Wutherium;
 ④ ......
-Synthesize các điểm trên, có thể kết luận rằng khu vực này không phù hợp để xây dựng khu định cư mới do các chỉ số vượt quá tiêu chuẩn môi trường sống.</t>
+Tổng hợp các điểm trên, có thể kết luận rằng khu vực này không phù hợp để xây dựng khu định cư mới do các chỉ số vượt quá tiêu chuẩn môi trường sống.</t>
         </is>
       </c>
     </row>
@@ -3412,11 +3406,11 @@
       <c r="M40" t="inlineStr">
         <is>
           <t>Phân tích quang phổ mẫu đất đã hoàn tất.
-Flower Shroom (Flower Shrooms) mọc ở khu vực này được nghiên cứu làm mẫu chính trong phân tích, và đã đưa ra các kết luận như sau:
+Nấm Hoa (Flower Shrooms) mọc ở khu vực này được nghiên cứu làm mẫu chính trong phân tích, và đã đưa ra các kết luận như sau:
 ① Đất ở đây có hàm lượng ẩm và chất hữu cơ cao;
 ② Đất bị lẫn một số tạp chất gây ô nhiễm;
 ③ ......
-Synthesize các điểm trên, có thể kết luận rằng khu vực này không phù hợp để xây dựng địa điểm mới do các chỉ số vượt quá tiêu chuẩn môi trường sống.</t>
+Tổng hợp các điểm trên, có thể kết luận rằng khu vực này không phù hợp để xây dựng địa điểm mới do các chỉ số vượt quá tiêu chuẩn môi trường sống.</t>
         </is>
       </c>
     </row>
@@ -3489,9 +3483,9 @@
           <t>Phân tích mẫu sinh vật đã hoàn tất.
 Trứng chim thu thập trong khu vực được nghiên cứu làm mẫu chính, kết luận như sau:
 ① Sinh vật sống trong khu vực có xu hướng năng động hơn, thậm chí có thể thể hiện mức độ hung hăng nhất định với con người;
-② Hàm lượng Hợp Chất Wutherium trong sinh vật sống tại đây vượt xa mức trung bình. Nghi ngờ Tacet Field gần đó đang hoạt động;
+② Hàm lượng Hợp Chất Wutherium trong sinh vật sống tại đây vượt xa mức trung bình. Nghi ngờ Tổ Tacet gần đó đang hoạt động;
 ③......
-Synthesize các điểm trên, có thể kết luận rằng khu vực này không phù hợp để xây dựng khu định cư mới do các chỉ số vượt quá tiêu chuẩn môi trường sống.</t>
+Tổng hợp các điểm trên, có thể kết luận rằng khu vực này không phù hợp để xây dựng khu định cư mới do các chỉ số vượt quá tiêu chuẩn môi trường sống.</t>
         </is>
       </c>
     </row>
@@ -3556,7 +3550,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Phỏng Vấn Sugar Phố bởi Tiancheng News: Tại sao lại là Hukou?</t>
+          <t>Phỏng Vấn Đường Phố bởi Tiancheng News: Tại sao lại là Hukou?</t>
         </is>
       </c>
     </row>
@@ -3624,10 +3618,10 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Phóng viên: Tôi có thể hỏi anh một câu không? Anh có biết tại sao nơi này được gọi là Hổ Khẩu, Tiger's Maw không?
-Công nhân lâu năm: Tiger's Maw à? À, hổ phải há miệng ra để ăn chứ!
+          <t>Phóng viên: Tôi có thể hỏi anh một câu không? Anh có biết tại sao nơi này được gọi là Hukou, Hàm Hổ không?
+Công nhân lâu năm: Hàm Hổ à? À, hổ phải há miệng ra để ăn chứ!
 Trẻ con: Vì ở đây có cái hang to như miệng hổ ấy! Grừừ...
-Passerby: Oai phong như hổ! À, bộ đồ của tôi là sư tử múa lân? Cũng na ná thôi mà...... (tiếng cười xung quanh)</t>
+Người qua đường: Oai phong như hổ! À, bộ đồ của tôi là sư tử múa lân? Cũng na ná thôi mà...... (tiếng cười xung quanh)</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3762,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>&lt;i&gt;Quy Tắc An Toàn Hukou Mine&lt;/i&gt;</t>
+          <t>&lt;i&gt;Quy Tắc An Toàn Mỏ Hukou&lt;/i&gt;</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3830,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Một số điều khoản mới được bổ sung vào &lt;i&gt;Quy Tắc An Toàn Hukou Mine&lt;/i&gt;:
+          <t>Một số điều khoản mới được bổ sung vào &lt;i&gt;Quy Tắc An Toàn Mỏ Hukou&lt;/i&gt;:
 43. Không tin vào những lời đồn về tiếng nói. Bạn không nên và sẽ không nghe thấy bất kỳ tiếng nói kỳ lạ nào trong mỏ, đặc biệt là tiếng của người thân đã khuất. (Không thể nào người đã qua đời lại nói chuyện với bạn được)
 44. Không được lại gần sương mù trong bất kỳ trường hợp nào, kể cả khi có ai đó gọi bạn trong sương.
 45. Nếu nghe thấy bất kỳ tiếng nói kỳ lạ nào, hãy phớt lờ nó. Ngừng ngay công việc đang làm và đến phòng y tế. Chúng tôi sẽ cung cấp phương pháp điều trị cho bạn, cả về tinh thần lẫn thể chất.</t>
@@ -3969,7 +3963,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Biên Bản Số 1 – Đội Thám Hiểm Hố Misty</t>
+          <t>Biên Bản Số 1 – Đội Thám Hiểm Hố Sương Mù</t>
         </is>
       </c>
     </row>
@@ -4107,7 +4101,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Biên Bản Số 2 của Đội Thám Hiểm vào Vực Misty</t>
+          <t>Biên Bản Số 2 của Đội Thám Hiểm vào Vực Sương Mù</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4233,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Biên Bản Số 3 của Đội Thám Hiểm vào Vực Misty</t>
+          <t>Biên Bản Số 3 của Đội Thám Hiểm vào Vực Sương Mù</t>
         </is>
       </c>
     </row>
@@ -4467,10 +4461,10 @@
 Jing: Không ổn rồi......
 Tan: Sao thế, sao thế?
 Jing: Thang máy này không chở ai cả. Tớ đã kiểm tra mấy tầng, chẳng có ai xung quanh...... Không, tớ phải ra ngoài xem sao.
-Tan: Eee ê, cậu không được tùy tiện như vậy. Nếu đây là một câu chuyện, thì ngoài kia có thể là bất cứ thứ gì đang chờ cậu đấy.
+Tan: Ê ê ê, cậu không được tùy tiện như vậy. Nếu đây là một câu chuyện, thì ngoài kia có thể là bất cứ thứ gì đang chờ cậu đấy.
 Jing: Không, giờ tớ đã nhận việc này rồi, không chỉ phải lo cho sự an toàn của bản thân. Còn cậu, một đại diện cho thế hệ mới của Tiancheng, lại nói chuyện như ông già cổ hủ vậy......
 Jing: Hay là do trục trặc máy móc, hoặc đồng nghiệp chơi khăm? Sau cùng, công việc ở mỏ chán ngắt, biết đâu họ đồng ý cho tớ, một thằng mới, một "bất ngờ"?
-A-tan: Cậu đúng là nhân vật chính trong truyện kinh dị! Unclec may mắn nhé, tớ sẽ cầu nguyện với Suiguang để cậu bình an......</t>
+A-tan: Cậu đúng là nhân vật chính trong truyện kinh dị! Chúc may mắn nhé, tớ sẽ cầu nguyện với Suiguang để cậu bình an......</t>
         </is>
       </c>
     </row>
@@ -4542,11 +4536,11 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Equip: Cáp Treo Chở Người và Hàng Hóa
+          <t>Trang Bị: Cáp Treo Chở Người và Hàng Hóa
 Số Seri: HLHk-09
-Đơn vị sử dụng: Phòng Vận Tải, Hukou Mine
+Đơn vị sử dụng: Phòng Vận Tải, Mỏ Hukou
 Mô tả lỗi: Dây cáp thép bị mòn và đứt bất thường, dẫn đến mất kết nối giữa các khoang cáp treo và khiến cáp không hoạt động bình thường.
-Xử lý: Replace dây cáp thép.
+Xử lý: Thay thế dây cáp thép.
 Nguyên nhân: Đã kiểm tra bánh kéo, ròng rọc dẫn hướng và bộ điều tốc, không phát hiện nguyên nhân. Nghi ngờ do thao tác sai.
 Khuyến cáo: Nếu bắt được ai nghịch ngợm chở quá tải trên cáp treo, tôi sẽ treo hắn lên dây cáp và cho hắn nếm trải cảm giác QUÁ TẢI!
 Người xử lý: Cheng</t>
@@ -4695,7 +4689,7 @@
 1. Nó không được bán ở chợ bình thường.
 2. Nó không chịu được va đập trong quá trình vận chuyển.
 3. Không thể lưu trữ lâu dài.
-4. Guan trọng nhất, đừng mở hộp Wutherium Fluid như mở đồ ăn đóng hộp. Điều này có thể giết chết bạn!</t>
+4. Quan trọng nhất, đừng mở hộp Wutherium Fluid như mở đồ ăn đóng hộp. Điều này có thể giết chết bạn!</t>
         </is>
       </c>
     </row>
@@ -4841,8 +4835,8 @@
         <is>
           <t>Ai bảo phải có nhạc cụ mới chơi nhạc được!
 Trong lúc làm việc ở mỏ, tôi luôn nghe thấy những âm thanh kỳ lạ, ban đầu tưởng đó là "tiếng nói" mà lời đồn nhắc đến... nhưng sau đó tôi phát hiện ra những âm thanh ấy thực ra phát ra từ Tacetite, và điều đáng kinh ngạc hơn là chúng có nhịp điệu riêng!
-Khi Tacetite được chuyển hóa thành Bức Xạ Wutherium trong Hộp Synergy, một phần dải tần số có thể nghe được bằng tai người. Hình dạng cắt gọt của Tacetite, tính chất quặng đều ảnh hưởng đến cách sóng âm này biến thành giai điệu.
-Tôi đã sắp xếp những âm thanh ghi lại suốt bao năm và biên soạn lại thành một bản nhạc, đó là "Sound of Stone" này.
+Khi Tacetite được chuyển hóa thành Bức Xạ Wutherium trong Hộp Cộng Hưởng, một phần dải tần số có thể nghe được bằng tai người. Hình dạng cắt gọt của Tacetite, tính chất quặng đều ảnh hưởng đến cách sóng âm này biến thành giai điệu.
+Tôi đã sắp xếp những âm thanh ghi lại suốt bao năm và biên soạn lại thành một bản nhạc, đó là "Âm Thanh Đá" này.
 Hy vọng một ngày nào đó, cách chơi nhạc mới mẻ này sẽ được mọi người yêu thích.</t>
         </is>
       </c>
@@ -4911,10 +4905,10 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Port Gunchao được thành lập vào năm 132 A.L., chủ yếu kinh doanh dịch vụ đại lý hàng hóa nội địa và quốc tế, cũng như đại lý tàu biển cho các mặt hàng như Tacetie thô, sản phẩm công nghiệp năng lượng, vật liệu âm thanh tiêu dùng, v.v. Với hệ thống quản lý container hàng đầu thế giới và cơ sở hạ tầng neo đậu tàu lớn, Port Gunchao là cảng trung chuyển tổng hợp và cảng container chính lớn nhất khu vực Huanglong.
-Chúng tôi đã hợp tác lâu dài và chặt chẽ với Hukou Mine và Pioneer Association, với chính sách giá cả công bằng, minh bạch và uy tín xuất sắc trong ngành.
+          <t>Cảng Gunchao được thành lập vào năm 132 A.L., chủ yếu kinh doanh dịch vụ đại lý hàng hóa nội địa và quốc tế, cũng như đại lý tàu biển cho các mặt hàng như Tacetie thô, sản phẩm công nghiệp năng lượng, vật liệu âm thanh tiêu dùng, v.v. Với hệ thống quản lý container hàng đầu thế giới và cơ sở hạ tầng neo đậu tàu lớn, Cảng Gunchao là cảng trung chuyển tổng hợp và cảng container chính lớn nhất khu vực Huanglong.
+Chúng tôi đã hợp tác lâu dài và chặt chẽ với Mỏ Hukou và Hiệp hội Pioneer, với chính sách giá cả công bằng, minh bạch và uy tín xuất sắc trong ngành.
 Chúng tôi hoan nghênh các đối tác từ mọi ngành nghề đến đàm phán kinh doanh.
-                                                                                              Văn Phòng Kinh Ying, Port Gunchao</t>
+                                                                                              Văn Phòng Kinh Doanh, Cảng Gunchao</t>
         </is>
       </c>
     </row>
@@ -4982,7 +4976,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>&lt;i&gt;A Diary Do Việc Tại Cảng&lt;/i&gt; Tác giả không rõ</t>
+          <t>&lt;i&gt;Nhật Ký Làm Việc Tại Cảng&lt;/i&gt; Tác giả không rõ</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5044,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Hi mừng đến với đường cao tốc. Dùng tuyến này để đến Port Gunchao, Hukou Mine và thành phố Tiancheng. Vui lòng xác nhận điểm đến của bạn.
+          <t>Chào mừng đến với đường cao tốc. Sử dụng tuyến này để đến Cảng Gunchao, Mỏ Hukou và thành phố Tiancheng. Vui lòng xác nhận điểm đến của bạn.
 Có thể bạn sẽ gặp những kẻ lưu vong hoặc MO dọc tuyến đường này. Hãy luôn cảnh giác và di chuyển cẩn thận khi vận chuyển hàng hóa qua đây.
 (T. B., xin đừng làm hư hại các cơ sở vật chất trên đường cao tốc, nếu không bạn có thể bị truy cứu trách nhiệm)
                                                                                                     Bảo trì: Đội 7, Bộ Phát Triển</t>
@@ -5124,7 +5118,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Mẫu đơn xin cấp vật tư
+          <t>Mẫu Đơn Xin Cấp Vật Tư
 Tên: Yizhu (ví dụ)
 Đơn vị trực thuộc: Bộ Phát Triển (ví dụ)
 Vật tư xin cấp &amp; Số lượng: 10 tác nhân giả TD hiện đại (ví dụ)
@@ -5407,9 +5401,9 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Scenario 7, 𝘕𝘩ữ𝘯𝘨 𝘎𝘩𝘪 𝘊𝘩é𝘱 𝘛𝘳𝘶𝘯𝘨 𝘛𝘩ą𝘮 𝘥𝘰 𝘝ề 𝘊𝘰𝘯 𝘛𝘢𝘯 𝘛𝘩ą𝘯𝘨 𝘊ủ𝘢 𝘑𝘪 𝘛𝘪𝘯𝘨, 𝘈.𝘓. 104
+          <t>Chương 7, 𝘕𝘩ữ𝘯𝘨 𝘎𝘩𝘪 𝘊𝘩é𝘱 𝘛𝘳𝘶𝘯𝘨 𝘛𝘩ą𝘮 𝘥𝘰 𝘝ề 𝘊𝘰𝘯 𝘛𝘢𝘯 𝘛𝘩ą𝘯𝘨 𝘊ủ𝘢 𝘑𝘪 𝘛𝘪𝘯𝘨, 𝘈.𝘓. 104
 Một khu định cư đơn sơ được xây dựng trên nền tảng của một cơ sở quân sự đã hoàn toàn không còn khả năng sinh sống sau thảm họa.
-Môi trường vẫn còn khắc nghiệt. Mist dày đặc thường xuyên bao phủ, trong khi chỉ số Wutheron liên tục xuất hiện bất thường.
+Môi trường vẫn còn khắc nghiệt. Sương mù dày đặc thường xuyên bao phủ, trong khi chỉ số Wutheron liên tục xuất hiện bất thường.
 Do hậu quả của việc cướp bóc thường xuyên từ những kẻ lưu đày hoạt động quanh đây, không còn gì có giá trị được tìm thấy trong khu vực.</t>
         </is>
       </c>
@@ -5480,12 +5474,12 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Năm 157 A.L., cuộc tấn công Tacet Field lớn nhất mang tên "Shui Triều Của Loài Thú" đã xuất hiện, đe dọa trực tiếp vào trung tâm Tiancheng.
+          <t>Năm 157 A.L., cuộc tấn công Tổ Tacet lớn nhất mang tên "Thủy Triều Của Loài Thú" đã xuất hiện, đe dọa trực tiếp vào trung tâm Thiên Thành.
 Vì sự sống còn của nhân loại, toàn quân Huanglong đã dốc hết sức lực, đoàn kết chống lại kẻ thù từ tuyến đầu cuối cùng.
-Trong số đó, Tiểu Đoàn Vanguard của Midnight Rangers đã xâm nhập sâu vào vùng lõi hoang dã, cố gắng tiêu diệt kẻ địch bằng chiến thuật cơ động. Họ đã phải trả giá đắt để đảo ngược tình thế từ thế phòng thủ bị động sang thế tấn công, hứa hẹn một chiến thắng cuối cùng cho Huanglong.
-Trong ký ức sâu thẳm nhất, 306 chiến binh đã ngã xuống trong trận Shui Triều Của Loài Thú được tưởng nhớ và tôn vinh tại nghĩa trang này.
+Trong số đó, Tiểu Đoàn Tiền Phong của Midnight Rangers đã xâm nhập sâu vào vùng lõi hoang dã, cố gắng tiêu diệt kẻ địch bằng chiến thuật cơ động. Họ đã phải trả giá đắt để đảo ngược tình thế từ thế phòng thủ bị động sang thế tấn công, hứa hẹn một chiến thắng cuối cùng cho Huanglong.
+Trong ký ức sâu thẳm nhất, 306 chiến binh đã ngã xuống trong trận Thủy Triều Của Loài Thú được tưởng nhớ và tôn vinh tại nghĩa trang này.
                                                                                                                                                                 TOÀN THỂ CHIẾN SĨ HUANGLONG
-Re bút: Năm 159 A.L., sau khi nghĩa trang được xây dựng, sự tụ họp của những người đến viếng và ký ức đau thương của họ đã gây ra một sự nhiễu loạn Wutheron trong khu vực, hình thành một Tacet Field nhỏ. Các phần của nghĩa trang đều chịu thiệt hại ở mức độ khác nhau. Dù có kế hoạch sửa chữa, người dân vẫn mong muốn giữ lại những dấu vết tàn phá này như một lời cảnh tỉnh và lời nhắc nhở về khủng hoảng.</t>
+Tái bút: Năm 159 A.L., sau khi nghĩa trang được xây dựng, sự tụ họp của những người đến viếng và ký ức đau thương của họ đã gây ra một sự nhiễu loạn Wutheron trong khu vực, hình thành một Tổ Tacet nhỏ. Các phần của nghĩa trang đều chịu thiệt hại ở mức độ khác nhau. Dù có kế hoạch sửa chữa, người dân vẫn mong muốn giữ lại những dấu vết tàn phá này như một lời cảnh tỉnh và lời nhắc nhở về khủng hoảng.</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5544,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>A Diary Combat Số 6010: Bước Enter Mùa Thu</t>
+          <t>Nhật Ký Chiến Đấu Số 6010: Bước Vào Mùa Thu</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5680,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>A Diary Combat Số 6010: Battles Điểm 91.7</t>
+          <t>Nhật Ký Chiến Đấu Số 6010: Trận Chiến Điểm 91.7</t>
         </is>
       </c>
     </row>
@@ -5758,14 +5752,14 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>11 đêm chứng kiến cuộc chiến giành cao điểm 91.7. Đơn vị XXX của chúng ta mất 16 người, trong đó có phó chỉ huy. 7 thương nặng và 8 thương nhẹ. Plays biến trận chiến như sau:
+          <t>11 đêm chứng kiến cuộc chiến giành cao điểm 91.7. Đơn vị XXX của chúng ta mất 16 người, trong đó có phó chỉ huy. 7 thương nặng và 8 thương nhẹ. Diễn biến trận chiến như sau:
 Cuối tháng Mười Một, kẻ địch tấn công cao điểm 9.17—một nơi không tên. Sau nhiều ngày đêm giao tranh ác liệt, phần lớn bề mặt cao điểm đã rơi vào tay địch. Ngày 27 tháng Mười, chúng tôi nhận lệnh tham chiến để chi viện cho đồng minh.
 Dưới hỏa lực yểm trợ, đơn vị chúng tôi tổ chức 6 đợt phản công trong 8 giờ, nhưng đều thất bại trong việc đẩy lùi kẻ địch khỏi cao điểm.
 Sáng sớm ngày 28, địch mở một đợt phản kích bất thành dưới sự yểm trợ của hỏa lực pháo.
 Từ ngày 28 tháng Mười đến ngày 6 tháng Mười Một, quyền kiểm soát cao điểm đổi chủ vài lần, nhưng không bên nào giành được ưu thế quyết định.
-Night ngày 6 tháng Mười Một, đơn vị chúng tôi được thay thế bởi một đơn vị bạn do tổn thất hơn 70% quân số.
+Đêm ngày 6 tháng Mười Một, đơn vị chúng tôi được thay thế bởi một đơn vị bạn do tổn thất hơn 70% quân số.
 Tóm tắt trận chiến:
-Mailơng vong của đơn vị chủ yếu do hỏa lực tầm gần. Điều này, thứ nhất, chứng minh những nhận định về phòng thủ hỏa lực gián tiếp trong quân đội; thứ hai, cho thấy sự chuẩn bị chưa đầy đủ của đơn vị trước hỏa lực chéo tầm gần. Report chiến đấu chi tiết sẽ được đính kèm sau.</t>
+Thương vong của đơn vị chủ yếu do hỏa lực tầm gần. Điều này, thứ nhất, chứng minh những nhận định về phòng thủ hỏa lực gián tiếp trong quân đội; thứ hai, cho thấy sự chuẩn bị chưa đầy đủ của đơn vị trước hỏa lực chéo tầm gần. Báo cáo chiến đấu chi tiết sẽ được đính kèm sau.</t>
         </is>
       </c>
     </row>
@@ -5830,7 +5824,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>A Diary Combat Số 6010: Re Organize</t>
+          <t>Nhật Ký Chiến Đấu Số 6010: Tái Tổ Chức</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5895,7 @@
           <t>Hôm nay là ngày 8 tháng 11. Chúng tôi rút về hậu phương để tái vũ trang theo lệnh. Tiếng đại bác vẫn vọng về từ tần số 91.7. Không còn nghi ngờ gì nữa, cao nguyên kia sẽ là chìa khóa của toàn bộ trận chiến. Bên nào chiếm được nó sẽ nắm quyền kiểm soát.
 Trên mảnh đất cao nguyên chật hẹp ấy, thịt và máu đã trở thành tuyến phòng thủ vững chắc nhất. Tất cả thép đều phải quỳ gối trước chúng.
 May mà tôi không mượn bộ đồ mới của phó chỉ huy, ít ra anh ấy còn có thể trở về trong danh dự.
-Anh ấy từng kể tôi nghe một câu chuyện, mà theo lời anh, là do ông nội anh kể lại—rằng khi một người ra đi, linh hồn trở về sẽ được gió đưa về nơi thuộc về họ. Night đã khuya, không biết các đồng đội của tôi đã lên đường trở về chưa.</t>
+Anh ấy từng kể tôi nghe một câu chuyện, mà theo lời anh, là do ông nội anh kể lại—rằng khi một người ra đi, linh hồn trở về sẽ được gió đưa về nơi thuộc về họ. Đêm đã khuya, không biết các đồng đội của tôi đã lên đường trở về chưa.</t>
         </is>
       </c>
     </row>
@@ -5966,7 +5960,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>A Diary Combat Số 6010: Lại Lên Sugar</t>
+          <t>Nhật Ký Chiến Đấu Số 6010: Lại Lên Đường</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6094,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>A Diary Combat Số 6010: Đây Có Thể Là Lần Cuối</t>
+          <t>Nhật Ký Chiến Đấu Số 6010: Đây Có Thể Là Lần Cuối</t>
         </is>
       </c>
     </row>
@@ -6170,12 +6164,12 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Giọng nói Nữ: "Mẹ ơi, hôm nay là ngày thứ 47 của trận chiến này, và con vừa tròn 22 tuổi."
-Giọng nói Nữ: "47 ngày, từ một tân binh bình thường, con đã trở thành chỉ huy tạm thời."
-Giọng nói Nữ: "Kẻ địch ào tới như gián không ngừng nghỉ."
-Giọng nói Nữ: "Và chúng con không hề do dự nghiền nát chúng, như mọi khi."
+          <t>Giọng Nữ: "Mẹ ơi, hôm nay là ngày thứ 47 của trận chiến này, và con vừa tròn 22 tuổi."
+Giọng Nữ: "47 ngày, từ một tân binh bình thường, con đã trở thành chỉ huy tạm thời."
+Giọng Nữ: "Kẻ địch ào tới như gián không ngừng nghỉ."
+Giọng Nữ: "Và chúng con không hề do dự nghiền nát chúng, như mọi khi."
 [im lặng một lúc, hít thở sâu]
-Giọng nói Nữ: "Mẹ ơi, con sẽ trở về. Họ sẽ đưa con về. Đừng khóa cửa sổ nhé."</t>
+Giọng Nữ: "Mẹ ơi, con sẽ trở về. Họ sẽ đưa con về. Đừng khóa cửa sổ nhé."</t>
         </is>
       </c>
     </row>
@@ -6244,9 +6238,9 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>1. Ban xâm nhập khu vực Incineranur đối với nhân sự không được phép. Tự chịu rủi ro nếu vi phạm. Nhân sự được phép phải tuân thủ quy tắc ứng xử.
+          <t>1. Cấm xâm nhập khu vực Incineranur đối với nhân sự không được phép. Tự chịu rủi ro nếu vi phạm. Nhân sự được phép phải tuân thủ quy tắc ứng xử.
 2. Mọi hoạt động trong khu vực Incineranur phải được cấp phép và thực hiện với chứng nhận phù hợp.
-3. Thiết bị bảo hộ phải được sử dụng cẩn thận trước khi vào Incineranur. Synergy Giả phải đồng thời mang và đeo thiết bị cách ly cùng bộ hấp thụ sóng; người không phải Synergy Giả không được vào trừ trường hợp cần thiết. Trong những tình huống đặc biệt, phải mặc thêm đồ bảo hộ chính xác.
+3. Thiết bị bảo hộ phải được sử dụng cẩn thận trước khi vào Incineranur. Resonator phải đồng thời mang và đeo thiết bị cách ly cùng bộ hấp thụ sóng; người không phải Resonator không được vào trừ trường hợp cần thiết. Trong những tình huống đặc biệt, phải mặc thêm đồ bảo hộ chính xác.
 4. Thời gian hoạt động trong khu vực Incineranur không được vượt quá 3 giờ. Nếu có bất kỳ dấu hiệu khó chịu về thể chất hay tinh thần trong quá trình hoạt động, phải rời đi ngay lập tức và tiến hành kiểm tra y tế.
 5. Nhân sự tham gia hoạt động dài hạn trong khu vực phải được đánh giá tâm lý định kỳ để tránh suy giảm tinh thần tiềm ẩn.</t>
         </is>
@@ -6389,7 +6383,7 @@
           <t>Dạo này trời ẩm ướt. Có thể sẽ có mưa ngược, nên tôi tìm được một mảnh vỡ vũ khí để che thân.
 Tại đó, tôi gặp một cặp anh em đang nghỉ ngơi. Hai đứa trẻ, cảnh giác với người lạ. Trông như vừa bỏ nhà ra đi.
 Tôi định gọi lính Morn từ trại đến đưa chúng về, nhưng chúng lao tới gần tôi, suýt chạm vào vành mũ.
-"Please, chú đừng báo người đến bắt chúng cháu. Em gái cháu và cháu chỉ muốn đi xem cánh đồng hoa thôi." Thằng bé to con hơn nhìn tôi tha thiết, khiến tôi lưỡng lự.
+"Làm ơn, chú đừng báo người đến bắt chúng cháu. Em gái cháu và cháu chỉ muốn đi xem cánh đồng hoa thôi." Thằng bé to con hơn nhìn tôi tha thiết, khiến tôi lưỡng lự.
 Cuối cùng, tôi cũng xiêu lòng. Ai chẳng tò mò khi còn trẻ? Bản thân tôi khi ấy cũng chẳng tìm được gì, sao không giúp chúng một chút. Cứ coi như thử vận may ở Incineranur vậy.</t>
         </is>
       </c>
@@ -6458,7 +6452,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Chúng tôi dừng lại ở rìa Incineranur, hai đứa trẻ gật đầu với nhau như thể xác nhận điều gì đó. Rồi cậu bé lấy ra một chiếc hộp nhỏ xinh từ ba lô, do dự trong giây lát trước khi Dodgem thứ bên trong hộp vào Incineranur.
+          <t>Chúng tôi dừng lại ở rìa Incineranur, hai đứa trẻ gật đầu với nhau như thể xác nhận điều gì đó. Rồi cậu bé lấy ra một chiếc hộp nhỏ xinh từ ba lô, do dự trong giây lát trước khi ném thứ bên trong hộp vào Incineranur.
 Chẳng mấy chốc, chiếc thiết bị dài kia tan chảy vào hư vô trong sức nóng cháy bỏng, và khi tôi quay đầu lại, hai đứa trẻ đang gào khóc.
 Than ôi, ta đã đi khắp thế gian mà chẳng sợ điều gì, chỉ riêng tiếng trẻ con khóc là đủ khiến ta nao lòng. May mà ta còn giữ con búp bê bị thổi bay trong hộp châu báu. Ta lấy nó ra và dỗ dành hai đứa nhỏ nín khóc.
 Dù món đồ chơi cũ kỹ này không thể vào được tòa tháp, nhưng cũng không uổng phí.</t>
@@ -6532,7 +6526,7 @@
       <c r="M84" t="inlineStr">
         <is>
           <t>Trên đường đưa bọn trẻ về, Annalica gửi cho tôi một bức ảnh độ phân giải cực thấp, nói đó là hình chiếc "đàn piano bỏ túi" mà cô bé đã cố công tìm được.
-Thật sự không ngờ... đó lại chính là món đồ vừa bị Dodgem vào Lò Thiêu Hóa, một bảo vật lịch sử! Đã hóa tro ngay trước mắt tôi!
+Thật không ngờ... đó lại chính là món đồ vừa bị ném vào Lò Thiêu Hóa, một bảo vật lịch sử! Đã hóa tro ngay trước mắt tôi!
 "Đó là kỷ vật tình yêu của ông và bà." Cô bé nói.
 "Đúng vậy! Ông bảo rằng trong chiến tranh, ông và bà bị lạc trong đám đông và nơi họ chia tay chính là cánh đồng hoa. Ông còn nói..." cậu bé sắp khóc nấc lên, "ông bảo nếu một ngày ông cũng ra đi, chúng ta hãy đặt chiếc đàn piano bỏ túi vào cánh đồng hoa để ông có thể chơi đàn cho bà nghe lần nữa."
 "Nhưng... nhưng con nghe bố nói hôm nay là nó có thể bán được giá cao lắm! Bố định bán nó mà, hu hu..."
@@ -6745,7 +6739,7 @@
       <c r="M87" t="inlineStr">
         <is>
           <t>Ngày: 08/01/157 A.L.
-Nội dung: Hôm nay, Trưởng nhóm lại nói chuyện với tôi. Ông ấy muốn tôi đưa ra ý kiến dứt khoát, với tư cách là trụ cột công nghệ - liệu chúng ta có nên tiếp tục khảo sát hay không. Tôi, ông ấy, và hầu như tất cả mọi người đều biết rằng kênh đào này có ý nghĩa lớn lao đến thế nào, và chúng ta đã trả giá đắt ra sao. Nếu dừng lại ở đây, thành quả bao năm sẽ đổ sông đổ biển. Nhưng nếu tiếp tục, cái giá phải trả có lẽ là mạng sống... Tôi không thể thuyết phục bản thân, cũng chẳng thuyết phục được đồng đội, những người đang sợ hãi trước những đợt sóng Tacet Field.</t>
+Nội dung: Hôm nay, Đội trưởng lại nói chuyện với tôi. Ông ấy muốn tôi đưa ra ý kiến dứt khoát, với tư cách là trụ cột công nghệ - liệu chúng ta có nên tiếp tục khảo sát hay không. Tôi, ông ấy, và hầu như tất cả mọi người đều biết rằng kênh đào này có ý nghĩa lớn lao đến thế nào, và chúng ta đã trả giá đắt ra sao. Nếu dừng lại ở đây, thành quả bao năm sẽ đổ sông đổ biển. Nhưng nếu tiếp tục, cái giá phải trả có lẽ là mạng sống... Tôi không thể thuyết phục bản thân, cũng chẳng thuyết phục được đồng đội, những người đang sợ hãi trước những đợt sóng Tổ Tacet.</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6808,7 @@
       <c r="M88" t="inlineStr">
         <is>
           <t>Ngày làm việc: 11/10/155 A.L.
-Tóm tắt công việc: Bản đồ phân bổ đơn vị khảo sát được lập để xác định vị trí chính của kênh đào. Gặp một đợt sóng Tacet Field nhỏ trong quá trình thu thập thông tin hình ảnh. Hai thành viên bị thương nhẹ sau khi được hỗ trợ kịp thời từ đại đội đặc nhiệm Ranger, dù thiết bị khảo sát bị hư hại nghiêm trọng.
+Tóm tắt công việc: Bản đồ phân bổ đơn vị khảo sát được lập để xác định vị trí chính của kênh đào. Gặp một đợt sóng Tổ Tacet nhỏ trong quá trình thu thập thông tin hình ảnh. Hai thành viên bị thương nhẹ sau khi được hỗ trợ kịp thời từ đại đội đặc nhiệm Ranger, dù thiết bị khảo sát bị hư hại nghiêm trọng.
 &lt;i&gt;Dự kiến thiết bị dự phòng sẽ đến trong một tuần, trước đó mọi công tác khảo sát tạm dừng.&lt;/i&gt;
 Ghi chú và nhận xét: Phát hiện mỏ quặng thô từ loại đá chưa xác định trong khu vực, cần khai quật và kiểm tra cấu trúc cũng như tính chất để đánh giá giá trị. Mối nguy hiểm đối với công tác xây dựng và khảo sát ở đây là đáng kể. Nếu có bất kỳ tình huống bất thường nào xảy ra, công việc phải lập tức dừng lại, nhân sự rút lui và thông báo cho Midnight Ranger.</t>
         </is>
@@ -6889,15 +6883,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>&lt;b&gt;[Thông báo mới]&lt;/b&gt;
-Ngày: 157 A.L.
-Nội dung: Do sự xuất hiện thường xuyên của sóng TD và mật độ Wutheron bất thường, việc điêu khắc Suiguang và khai quật kênh đào tạm ngừng từ thời điểm này. Tất cả nhân viên của Bộ Phát Triển và Midnight Ranger được lệnh rút khỏi khu vực. Thời gian tiếp tục chưa được xác định.
-&lt;b&gt;[Thông báo cũ]&lt;/b&gt;
-Ngày: 154 A.L.
-Nội dung: Hôm nay, lối vào Gorges of Spirit đã được thông suốt, nơi các đơn vị đặc biệt của Midnight Ranger gặp phải những đợt sóng TD tích tụ với mức độ nguy hiểm đặc biệt. Số liệu về tử vong, thương tích nặng và mất tích vẫn chưa được ghi nhận do quá cao. Jiyan được bổ nhiệm làm chỉ huy tạm thời sau sự hy sinh anh dũng của người tiền nhiệm.
-&lt;b&gt;[[Thông báo cũ]&lt;/b&gt;
-Ngày: 140 A.L.
-Nội dung: Theo ủy nhiệm của Bộ, một đơn vị đặc biệt của Midnight Ranger sẽ chịu trách nhiệm nghiên cứu và dọn dẹp các lô đất tại Gorges of Spirit để Bộ có thể tiến hành khảo sát chi tiết hơn. Dự kiến ban đầu cho thấy lối vào Gorges sẽ được mở trước năm 150 A.L..</t>
+          <t>&lt;b&gt;[Thông Báo Mới Nhất]&lt;/b&gt;</t>
         </is>
       </c>
     </row>
@@ -6968,8 +6954,8 @@
         <is>
           <t>Độ Cứng: cấp 6
 Mật độ: 3,0-3,5g/cm³
-Intensity chịu Dodgen: 3000-5000kg/cm³
-Templates vật có tên Xxx sở hữu cấu trúc tinh xảo, độ cứng và khả năng chịu Dodgen tốt, cùng tính ổn định hóa học đáng tin cậy. Nó có thể chịu được những biến đổi nhiệt độ khắc nghiệt.
+Cường độ chịu nén: 3000-5000kg/cm³
+Mẫu vật có tên Xxx sở hữu cấu trúc tinh xảo, độ cứng và khả năng chịu nén tốt, cùng tính ổn định hóa học đáng tin cậy. Nó có thể chịu được những biến đổi nhiệt độ khắc nghiệt.
 Xxx phân bố rộng rãi tại Gorges of Spirit với trữ lượng dồi dào, thuận tiện cho việc khai thác, và có xác suất cao tìm thấy những mỏ lớn. Đây là vật liệu xây dựng xuất sắc, phù hợp cho các tác phẩm điêu khắc lớn, tường ngoài và lớp phủ cứng.</t>
         </is>
       </c>
@@ -7037,7 +7023,7 @@
       <c r="M91" t="inlineStr">
         <is>
           <t>Ngày: 154 A.L.
-Nội dung: Trong chiến dịch tái chiếm Gorges of Spirit, Midnight Ranger phải đối mặt với điều kiện cực kỳ bất lợi do chỉ huy trưởng tử trận và lực lượng không cân xứng. Tuy nhiên, nhờ sự phục vụ xuất sắc của Jiyan, một trong những chiến binh của chúng ta, đại đội đặc nhiệm duy nhất còn lại đã chống trả các đợt sóng Tacet Field quy mô lớn trong 3 ngày và giữ vững vị trí cho đến khi lực lượng chủ lực đến tiếp viện. Các lực lượng sau đó đã phối hợp và chỉ huy đánh bại Tacet Field thành công. Hầu hết kết quả điều tra do đó được bảo toàn.</t>
+Nội dung: Trong chiến dịch tái chiếm Gorges of Spirit, Midnight Ranger phải đối mặt với điều kiện cực kỳ bất lợi do chỉ huy trưởng tử trận và lực lượng không cân xứng. Tuy nhiên, nhờ sự phục vụ xuất sắc của Jiyan, một trong những chiến binh của chúng ta, đại đội đặc nhiệm duy nhất còn lại đã chống trả các đợt sóng Tổ Tacet quy mô lớn trong 3 ngày và giữ vững vị trí cho đến khi lực lượng chủ lực đến tiếp viện. Các lực lượng sau đó đã phối hợp và chỉ huy đánh bại Tổ Tacet thành công. Hầu hết kết quả điều tra do đó được bảo toàn.</t>
         </is>
       </c>
     </row>
@@ -7102,7 +7088,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>&lt;i&gt;Báo Cáo Investigate Gorges of Spirit&lt;/i&gt;</t>
+          <t>&lt;i&gt;Báo Cáo Điều Tra Gorges of Spirit&lt;/i&gt;</t>
         </is>
       </c>
     </row>
@@ -7172,9 +7158,9 @@
       <c r="M93" t="inlineStr">
         <is>
           <t>[Tiếng ồn từ Thiết bị Liên lạc]
-Yesterday đã liên lạc với gia đình. Con gái tôi lẩm bẩm mấy lần rằng muốn được tận mắt thấy thác nước lớn và con rùa khổng lồ, muốn được nhìn chúng ở chính nơi chúng đang ở.
+Hôm qua đã liên lạc với gia đình. Con gái tôi lẩm bẩm mấy lần rằng muốn được tận mắt thấy thác nước lớn và con rùa khổng lồ, muốn được nhìn chúng ở chính nơi chúng đang ở.
 Ôi trời đất... Tôi phải thương lượng mãi nó mới chịu chỉ xem ảnh thôi.
-Lạ thật, nơi này không bị Tacet Field tàn phá nhiều, có lẽ nhờ con quái vật to lớn đang ngự trị dưới hồ này.
+Lạ thật, nơi này không bị Tổ Tacet tàn phá nhiều, có lẽ nhờ con quái vật to lớn đang ngự trị dưới hồ này.
 Tôi cũng phải cẩn thận đừng để làm nó giật mình.</t>
         </is>
       </c>
@@ -7240,7 +7226,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>&lt;i&gt;Chương 1, Suối Fangdong và Kinh Điển Phương Tây&lt;/i&gt;</t>
+          <t>&lt;i&gt;Chương 1, Suối Phương Đông và Kinh Điển Phương Tây&lt;/i&gt;</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7306,7 @@
       <c r="M95" t="inlineStr">
         <is>
           <t>Fella: anh bạn, đồng chí.
-Make yourself known: Malee ngươi là gì.
+Make yourself known: Tên mày là gì.
 Hide the blade: không tiện nói tên.
 Big known: Người nổi danh.
 Emp: Thằng ngơ mới vào nghề.
@@ -7331,7 +7317,7 @@
 Peeker: Con mắt.
 Wind-taker: Lỗ tai.
 Gold pole: Cái chân.
-The green: Weapons.
+The green: Vũ khí.
 The stick: Súng.
 ...</t>
         </is>
@@ -7405,14 +7391,14 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Tân Lịch năm 110 - Thú thần Tuế Guang đánh bại Minh Thức, một cô gái tên Tân Di nhờ tia lửa hy vọng nhỏ bé đã thắp lại niềm tin trong lòng mọi người. Cô đã phát biểu đầy hứng khởi tại một nơi trú ẩn tạm thời, khơi dậy làn sóng tái thiết Hoàng Long khắp nơi. Tân Di dẫn dắt mọi người bắt đầu bước đầu tái thiết quanh khu vực núi Thừa Tiêu - nơi thú thần yên nghỉ.
-Tân Lịch năm 115 - Qua tính toán của trung tâm diễn toán Minh Vực, vị trí của Tân Đô được xác định, chính là nơi Tiancheng tọa lạc hiện nay.
-Tân Lịch năm 116 - Ngày đầu năm mới, Tân Đô Tiancheng chính thức khởi công xây dựng.
-Tân Lịch năm 120 - Tiancheng hoàn thành giai đoạn xây dựng đầu tiên, phần lớn cư dân từ khắp nơi di cư về đây, sau đó hàng chục năm cơ sở hạ tầng của Tiancheng dần được hoàn thiện.
-Tân Lịch năm 134 - Tiancheng lần đầu hứng chịu cuộc tấn công của bầy Ảo Tượng Thú, sau đó các đợt tấn công liên tiếp xảy ra, đến nay vẫn là một trong những mối nguy lớn đe dọa Hoàng Long.
-Tân Lịch năm 155 - Để cổ vũ tinh thần, lễ tuyên dương Tứ Kiệt Hoàng Long được tổ chức. Cùng năm, Jin Tịch - người cộng hưởng với thú thần Tuế Guang - trở thành Tân Chủ Long.
-Tân Lịch năm 157 - Hoàng Long hứng chịu đợt tấn công Ảo Tượng lớn nhất kể từ khi tái thiết, được gọi là "Sóng Impulse Predator". Trận chiến này gây tổn thất nặng nề, cuối cùng nhờ Jin Tịch đánh thức Tuế Guang mới bảo vệ được Tiancheng tái thiết.
-Hiện nay, Hoàng Long đang dần hồi phục sau vết thương, Tiancheng đã trở thành nơi gửi gắm hy vọng của tất cả người dân Hoàng Long.</t>
+          <t>Tân Lịch năm 110 - Thú thần Tuế Quang đánh bại Minh Thức, một cô gái tên Tân Di nhờ tia lửa hy vọng nhỏ bé đã thắp lại niềm tin trong lòng mọi người. Cô đã phát biểu đầy hứng khởi tại một nơi trú ẩn tạm thời, khơi dậy làn sóng tái thiết Hoàng Long khắp nơi. Tân Di dẫn dắt mọi người bắt đầu bước đầu tái thiết quanh khu vực núi Thừa Tiêu - nơi thú thần yên nghỉ.
+Tân Lịch năm 115 - Qua tính toán của trung tâm diễn toán Minh Vực, vị trí của Tân Đô được xác định, chính là nơi Thiên Thành tọa lạc hiện nay.
+Tân Lịch năm 116 - Ngày đầu năm mới, Tân Đô Thiên Thành chính thức khởi công xây dựng.
+Tân Lịch năm 120 - Thiên Thành hoàn thành giai đoạn xây dựng đầu tiên, phần lớn cư dân từ khắp nơi di cư về đây, sau đó hàng chục năm cơ sở hạ tầng của Thiên Thành dần được hoàn thiện.
+Tân Lịch năm 134 - Thiên Thành lần đầu hứng chịu cuộc tấn công của bầy Ảo Tượng Thú, sau đó các đợt tấn công liên tiếp xảy ra, đến nay vẫn là một trong những mối nguy lớn đe dọa Hoàng Long.
+Tân Lịch năm 155 - Để cổ vũ tinh thần, lễ tuyên dương Tứ Kiệt Hoàng Long được tổ chức. Cùng năm, Kim Tịch - người cộng hưởng với thú thần Tuế Quang - trở thành Tân Chủ Long.
+Tân Lịch năm 157 - Hoàng Long hứng chịu đợt tấn công Ảo Tượng lớn nhất kể từ khi tái thiết, được gọi là "Sóng Thú Dữ Dội". Trận chiến này gây tổn thất nặng nề, cuối cùng nhờ Kim Tịch đánh thức Tuế Quang mới bảo vệ được Thiên Thành tái thiết.
+Hiện nay, Hoàng Long đang dần hồi phục sau vết thương, Thiên Thành đã trở thành nơi gửi gắm hy vọng của tất cả người dân Hoàng Long.</t>
         </is>
       </c>
     </row>
@@ -7482,7 +7468,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>&lt;i&gt;Phiếu Mailởng Carnival Ẩm Thực Tiancheng - Phiếu Há Cảo&lt;/i&gt;</t>
+          <t>&lt;i&gt;Phiếu Thưởng Lễ Hội Ẩm Thực Tiancheng - Phiếu Há Cảo&lt;/i&gt;</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7533,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>A Diary Bí Mật Số 1</t>
+          <t>Nhật Ký Bí Mật Số 1</t>
         </is>
       </c>
     </row>
@@ -7683,7 +7669,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>A Diary Bí Mật Số 2</t>
+          <t>Nhật Ký Bí Mật Số 2</t>
         </is>
       </c>
     </row>
@@ -7829,13 +7815,13 @@
           <t>Ngày: Tân Lịch năm 159
 Mức độ bảo mật: S
 Biên bản vụ án:
-Tân Lịch năm 159, Trưởng nhóm Tiểu vệ Tự Guan bị ám sát bên ngoài Trung khu Chỉ huy, cấp cứu không kịp và tử vong.
-Qua điều tra, hiện trường có dấu vết giao tranh rõ ràng, đêm đó nhiều người nhìn thấy ánh lửa kèm theo tiếng nổ, dựa trên phân tích dữ liệu còn sót lại, nghi phạm là một Synergy Giả sở hữu năng lực dị thường.
+Tân Lịch năm 159, Đội trưởng Tiểu vệ Tự Quan bị ám sát bên ngoài Trung khu Chỉ huy, cấp cứu không kịp và tử vong.
+Qua điều tra, hiện trường có dấu vết giao tranh rõ ràng, đêm đó nhiều người nhìn thấy ánh lửa kèm theo tiếng nổ, dựa trên phân tích dữ liệu còn sót lại, nghi phạm là một Cộng Hưởng Giả sở hữu năng lực dị thường.
 Khi đội tuần tra Tiểu vệ đến nơi, nghi phạm đã biến mất, phong tỏa tất cả lối vào thành đều không phát hiện người khả nghi, nghi phạm được cho là có phương thức di chuyển khác thường.
-Trong tay Trưởng nhóm Tự Guan còn sót lại mảnh vỡ màu đỏ, nghi là manh mối, nhưng do mảnh vỡ quá nhỏ nên chưa thể xác định mục tiêu.
+Trong tay Đội trưởng Tự Quan còn sót lại mảnh vỡ màu đỏ, nghi là manh mối, nhưng do mảnh vỡ quá nhỏ nên chưa thể xác định mục tiêu.
 Vụ việc trọng đại, đề xuất tạm thời không công khai chi tiết vụ án, chuyển sang điều tra bí mật.
-Uncle thích của Jin Tịch:
-Đồng ý. Trưởng nhóm Tự Guan được tin tưởng sâu sắc, việc này có thể gây chấn động lòng người, dẫn đến hoảng loạn, cần làm tốt công tác trấn an.</t>
+Chú thích của Kim Tịch:
+Đồng ý. Đội trưởng Tự Quan được tin tưởng sâu sắc, việc này có thể gây chấn động lòng người, dẫn đến hoảng loạn, cần làm tốt công tác trấn an.</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7888,7 @@
       <c r="M103" t="inlineStr">
         <is>
           <t>Bức tranh dài 400 cm, rộng 30 cm, nhiều chỗ hư hại, khó nhận diện nội dung.
-Left có ba vết sửa chữa, phần đã phục chế hiện lên khung cảnh phố thị tấp nập, đông vui, cửa hàng san sát, xe cộ qua lại tấp nập, nhắm mắt lại như thể đang lạc vào giữa khung cảnh ấy, tiếng người ồn ào náo nhiệt vẫn văng vẳng bên tai.</t>
+Bên trái có ba vết sửa chữa, phần đã phục chế hiện lên khung cảnh phố thị tấp nập, đông vui, cửa hàng san sát, xe cộ qua lại tấp nập, nhắm mắt lại như thể đang lạc vào giữa khung cảnh ấy, tiếng người ồn ào náo nhiệt vẫn văng vẳng bên tai.</t>
         </is>
       </c>
     </row>
@@ -7981,9 +7967,9 @@
 Bộ tranh khai quật từ di tích cổ này còn bảo quản khá tốt, chỉ có 47 điểm hư hại.
 Bức tranh cuộn dài này khá thú vị, ghi lại lối sống của một vùng đất bằng phong cách tranh cuộn ngang, trong đó có những điều mà mọi người chưa từng nghe thấy. Nếu sửa chữa xong, chắc chắn sẽ hé lộ được những mảnh thời gian trước khi Bi Minh xảy ra.
 Phản hồi ẩn danh:
-Dish ở gian hàng thứ ba bên trái trông ngon quá, ghi lại để nhờ cô Phàn Hoa thử làm xem sao.
+Món ăn ở gian hàng thứ ba bên trái trông ngon quá, ghi lại để nhờ cô Phàn Hoa thử làm xem sao.
 À, còn món đồ trang trí trước gian hàng thứ sáu, là... đồ chơi à?
-Người dân vùng này thật thú vị! Hy vọng lần lễ hội tới có thể trưng bày bức tranh này ở Tiancheng!</t>
+Người dân vùng này thật thú vị! Hy vọng lần lễ hội tới có thể trưng bày bức tranh này ở Thiên Thành!</t>
         </is>
       </c>
     </row>
@@ -8051,7 +8037,7 @@
       <c r="M105" t="inlineStr">
         <is>
           <t>Bức tranh cuộn ngang, cảnh sắc sông nước mênh mông, núi non trùng điệp bằng mực tàu.
-Nhờ những bức ảnh về tranh vẽ trước Bi Minh do ông Chenpi cung cấp, quá trình phục chế tác phẩm này diễn ra suôn sẻ và hiệu quả.
+Nhờ những bức ảnh về tranh vẽ trước Bi Minh do ông Trần Bì cung cấp, quá trình phục chế tác phẩm này diễn ra suôn sẻ và hiệu quả.
 Chủ Long đặt tên là *Văn Dã*, dự định trưng bày toàn thành vào Tân Lịch năm 160.</t>
         </is>
       </c>
@@ -8191,10 +8177,10 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>1: Milk Morricow có vị thật đặc biệt! Hơi cay, hơi tê, lại hơi đắng như cỏ dại, chắc có thể thay thế nguyên liệu cho trà sữa mặn đấy. Tôi có linh cảm loại trà sữa này sẽ gây sốt! Nếu ai cũng hứng thú với "Tea Milk Cay Nồng", hãy để lại bình luận, tôi sẽ đếm số lượng và tổ chức sự kiện thử nghiệm ở Tiancheng. Biết đâu chúng ta sẽ sản xuất đại trà.
+          <t>1: Sữa Morricow có vị thật đặc biệt! Hơi cay, hơi tê, lại hơi đắng như cỏ dại, chắc có thể thay thế nguyên liệu cho trà sữa mặn đấy. Tôi có linh cảm loại trà sữa này sẽ gây sốt! Nếu ai cũng hứng thú với "Trà Sữa Cay Nồng", hãy để lại bình luận, tôi sẽ đếm số lượng và tổ chức sự kiện thử nghiệm ở Tiancheng. Biết đâu chúng ta sẽ sản xuất đại trà.
 2: Tôi sẽ uống, tôi sẽ uống! Nghiện mất thôi.
-3: Cuộc đời tôi sẽ đi tong nếu không được uống Tea Milk Cay Nồng...
-4: Yi định phải tổ chức sự kiện thử nghiệm, vì cả nhà tôi sẽ đặt hàng!</t>
+3: Cuộc đời tôi sẽ đi tong nếu không được uống Trà Sữa Cay Nồng...
+4: Nhất định phải tổ chức sự kiện thử nghiệm, vì cả nhà tôi sẽ đặt hàng!</t>
         </is>
       </c>
     </row>
@@ -8282,30 +8268,30 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Ma Xiu: "Painter", bức tranh này là...?
-"Painter": Một món quà chia tay dành cho ngài, khắc họa khoảnh khắc ngài lìa đời.
+          <t>Ma Xiu: Họa sĩ, bức tranh này là...?
+Họa sĩ: Một món quà chia tay dành cho ngài, khắc họa khoảnh khắc ngài lìa đời.
 Ma Xiu: Ha ha ha ha! Một món quà chia tay độc đáo đến thế, quả là người kỳ lạ.
-"Painter": Tôi cứ ngỡ ngài sẽ giận dữ đôi chút.
+Họa sĩ: Tôi cứ ngỡ ngài sẽ giận dữ đôi chút.
 Ma Xiu: Từ khi có đứa con gái, tính tôi đã tốt lên không ngờ.
-"Painter": Nhắc đến tiểu thư, cô bé có vẻ khá yếu đuối.
+Họa sĩ: Nhắc đến tiểu thư, cô bé có vẻ khá yếu đuối.
 Ma Xiu: Sao ông lại nghĩ thế? Con bé luôn là đứa trẻ dũng cảm.
-"Painter": Cô bé không thích cái tên "Ma Tiểu Phương".
+Họa sĩ: Cô bé không thích cái tên "Ma Tiểu Phương".
 Ma Xiu: Điều đó chứng tỏ gì?
-"Painter": Chứng tỏ cô bé thậm chí còn thiếu cả dũng khí đối diện với chính mình.
+Họa sĩ: Chứng tỏ cô bé thậm chí còn thiếu cả dũng khí đối diện với chính mình.
 Ma Xiu: Đối diện với bản thân đâu phải chuyện đơn giản. Tôi hiểu con mình, một ngày nào đó, nó sẽ trở thành anh hùng dũng cảm nhất.
-"Painter": Nếu như nó có cơ hội cứu ngài, nhưng vì bản tính yếu đuối mà bỏ lỡ khoảnh khắc quyết định thì sao?
+Họa sĩ: Nếu như nó có cơ hội cứu ngài, nhưng vì bản tính yếu đuối mà bỏ lỡ khoảnh khắc quyết định thì sao?
 Ma Xiu: ……
-Ma Xiu: "Painter", ông nói thật đấy à?
-"Painter": Rất thật.
-Ma Xiu: "Painter" à, được chứng kiến tài tiên đoán kỳ diệu của ông là vinh hạnh của tôi. Nhưng về điểm này, tôi nghĩ ông đã sai.
-"Painter": Về cái chết của ngài?
+Ma Xiu: Họa sĩ, ông nói thật đấy à?
+Họa sĩ: Rất thật.
+Ma Xiu: Họa sĩ à, được chứng kiến tài tiên đoán kỳ diệu của ông là vinh hạnh của tôi. Nhưng về điểm này, tôi nghĩ ông đã sai.
+Họa sĩ: Về cái chết của ngài?
 Ma Xiu: Không, về đứa con của tôi.
 Ma Xiu: Nếu như mọi chuyện diễn ra đúng như lời ông nói, thì sự ra đi của tôi, chắc hẳn sẽ là khởi đầu cho con đường anh hùng của nó.
-"Painter": Tại sao vậy?
+Họa sĩ: Tại sao vậy?
 Ma Xiu: Tôi đã nói lý do rồi mà.
-"Painter": Huh
+Họa sĩ: Hử?
 Ma Xiu: Tôi hiểu con mình, một ngày nào đó, nó sẽ trở thành anh hùng dũng cảm nhất.
-"Painter": Ngài Ma Xiu, ngài cũng là một người kỳ lạ đấy...
+Họa sĩ: Ngài Ma Xiu, ngài cũng là một người kỳ lạ đấy...
 Vậy thì, chúng ta hãy cùng chờ xem.</t>
         </is>
       </c>
